--- a/results/table/30_aei_v6_structure.xlsx
+++ b/results/table/30_aei_v6_structure.xlsx
@@ -20,73 +20,307 @@
     <t>metric_id</t>
   </si>
   <si>
+    <t>ai_autonomy_mean</t>
+  </si>
+  <si>
+    <t>collaboration_bucket_automation_pct</t>
+  </si>
+  <si>
+    <t>collaboration_directive_pct</t>
+  </si>
+  <si>
+    <t>usage_per_capita_index</t>
+  </si>
+  <si>
+    <t>collaboration_none_pct</t>
+  </si>
+  <si>
     <t>usage_pct</t>
   </si>
   <si>
+    <t>human_education_years_mean</t>
+  </si>
+  <si>
+    <t>multitasking_pct</t>
+  </si>
+  <si>
+    <t>human_only_ability_pct</t>
+  </si>
+  <si>
+    <t>use_case_coursework_pct</t>
+  </si>
+  <si>
+    <t>collaboration_bucket_augmentation_pct</t>
+  </si>
+  <si>
     <t>use_case_work_pct</t>
   </si>
   <si>
+    <t>ai_education_years_mean</t>
+  </si>
+  <si>
+    <t>human_with_ai_time_mean</t>
+  </si>
+  <si>
+    <t>human_only_time_mean</t>
+  </si>
+  <si>
+    <t>collaboration_feedback_loop_pct</t>
+  </si>
+  <si>
+    <t>collaboration_validation_pct</t>
+  </si>
+  <si>
+    <t>collaboration_learning_pct</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>collaboration_task_iteration_pct</t>
+  </si>
+  <si>
+    <t>use_case_personal_pct</t>
+  </si>
+  <si>
+    <t>artifact_resume_or_job_application_pct</t>
+  </si>
+  <si>
+    <t>artifact_game_or_interactive_pct</t>
+  </si>
+  <si>
+    <t>artifact_ui_or_design_mockup_pct</t>
+  </si>
+  <si>
+    <t>artifact_presentation_or_slides_pct</t>
+  </si>
+  <si>
+    <t>artifact_none_pct</t>
+  </si>
+  <si>
+    <t>artifact_ml_or_ai_system_pct</t>
+  </si>
+  <si>
+    <t>artifact_image_or_graphic_pct</t>
+  </si>
+  <si>
+    <t>artifact_marketing_or_social_content_pct</t>
+  </si>
+  <si>
+    <t>artifact_document_or_report_pct</t>
+  </si>
+  <si>
+    <t>artifact_academic_paper_or_thesis_pct</t>
+  </si>
+  <si>
+    <t>artifact_math_or_calculation_pct</t>
+  </si>
+  <si>
+    <t>artifact_idea_or_brainstorm_pct</t>
+  </si>
+  <si>
+    <t>artifact_plan_or_strategy_pct</t>
+  </si>
+  <si>
+    <t>artifact_other_pct</t>
+  </si>
+  <si>
+    <t>artifact_app_or_website_pct</t>
+  </si>
+  <si>
+    <t>artifact_creative_writing_pct</t>
+  </si>
+  <si>
+    <t>artifact_explanation_or_answer_pct</t>
+  </si>
+  <si>
+    <t>artifact_code_fix_or_debug_pct</t>
+  </si>
+  <si>
+    <t>artifact_sql_or_database_query_pct</t>
+  </si>
+  <si>
+    <t>artifact_analysis_or_summary_pct</t>
+  </si>
+  <si>
+    <t>artifact_script_or_snippet_pct</t>
+  </si>
+  <si>
+    <t>artifact_config_or_infra_pct</t>
+  </si>
+  <si>
+    <t>artifact_data_or_spreadsheet_pct</t>
+  </si>
+  <si>
+    <t>artifact_blog_or_article_pct</t>
+  </si>
+  <si>
+    <t>artifact_translation_pct</t>
+  </si>
+  <si>
+    <t>artifact_chart_or_visualization_pct</t>
+  </si>
+  <si>
+    <t>artifact_advice_or_recommendation_pct</t>
+  </si>
+  <si>
+    <t>artifact_educational_material_pct</t>
+  </si>
+  <si>
+    <t>artifact_audio_or_music_pct</t>
+  </si>
+  <si>
+    <t>artifact_video_or_animation_pct</t>
+  </si>
+  <si>
+    <t>artifact_recipe_or_meal_plan_pct</t>
+  </si>
+  <si>
+    <t>artifact_email_or_message_pct</t>
+  </si>
+  <si>
+    <t>multitasking_pct</t>
+  </si>
+  <si>
+    <t>use_case_work_pct</t>
+  </si>
+  <si>
+    <t>use_case_coursework_pct</t>
+  </si>
+  <si>
+    <t>use_case_personal_pct</t>
+  </si>
+  <si>
+    <t>human_education_years_mean</t>
+  </si>
+  <si>
+    <t>collaboration_task_iteration_pct</t>
+  </si>
+  <si>
+    <t>usage_per_capita_index</t>
+  </si>
+  <si>
+    <t>ai_education_years_mean</t>
+  </si>
+  <si>
+    <t>human_with_ai_time_mean</t>
+  </si>
+  <si>
+    <t>ai_autonomy_mean</t>
+  </si>
+  <si>
+    <t>collaboration_bucket_augmentation_pct</t>
+  </si>
+  <si>
+    <t>collaboration_feedback_loop_pct</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>collaboration_none_pct</t>
+  </si>
+  <si>
     <t>human_only_ability_pct</t>
   </si>
   <si>
-    <t>use_case_personal_pct</t>
-  </si>
-  <si>
-    <t>multitasking_pct</t>
-  </si>
-  <si>
-    <t>human_education_years_mean</t>
-  </si>
-  <si>
-    <t>human_with_ai_time_mean</t>
-  </si>
-  <si>
     <t>collaboration_learning_pct</t>
   </si>
   <si>
+    <t>usage_pct</t>
+  </si>
+  <si>
+    <t>collaboration_directive_pct</t>
+  </si>
+  <si>
+    <t>human_only_time_mean</t>
+  </si>
+  <si>
     <t>collaboration_validation_pct</t>
   </si>
   <si>
-    <t>use_case_coursework_pct</t>
-  </si>
-  <si>
-    <t>collaboration_none_pct</t>
-  </si>
-  <si>
-    <t>collaboration_task_iteration_pct</t>
-  </si>
-  <si>
-    <t>collaboration_bucket_augmentation_pct</t>
-  </si>
-  <si>
     <t>collaboration_bucket_automation_pct</t>
   </si>
   <si>
-    <t>usage_per_capita_index</t>
-  </si>
-  <si>
-    <t>collaboration_feedback_loop_pct</t>
-  </si>
-  <si>
-    <t>collaboration_directive_pct</t>
-  </si>
-  <si>
-    <t>human_only_time_mean</t>
-  </si>
-  <si>
-    <t>pct</t>
-  </si>
-  <si>
-    <t>ai_autonomy_mean</t>
-  </si>
-  <si>
-    <t>ai_education_years_mean</t>
+    <t>artifact_video_or_animation_pct</t>
+  </si>
+  <si>
+    <t>artifact_chart_or_visualization_pct</t>
+  </si>
+  <si>
+    <t>artifact_code_fix_or_debug_pct</t>
+  </si>
+  <si>
+    <t>artifact_game_or_interactive_pct</t>
+  </si>
+  <si>
+    <t>artifact_sql_or_database_query_pct</t>
+  </si>
+  <si>
+    <t>artifact_data_or_spreadsheet_pct</t>
+  </si>
+  <si>
+    <t>artifact_none_pct</t>
+  </si>
+  <si>
+    <t>artifact_educational_material_pct</t>
+  </si>
+  <si>
+    <t>artifact_image_or_graphic_pct</t>
+  </si>
+  <si>
+    <t>artifact_other_pct</t>
+  </si>
+  <si>
+    <t>artifact_ml_or_ai_system_pct</t>
+  </si>
+  <si>
+    <t>artifact_analysis_or_summary_pct</t>
   </si>
   <si>
     <t>artifact_presentation_or_slides_pct</t>
   </si>
   <si>
-    <t>artifact_video_or_animation_pct</t>
+    <t>artifact_script_or_snippet_pct</t>
+  </si>
+  <si>
+    <t>artifact_creative_writing_pct</t>
+  </si>
+  <si>
+    <t>artifact_document_or_report_pct</t>
+  </si>
+  <si>
+    <t>artifact_explanation_or_answer_pct</t>
+  </si>
+  <si>
+    <t>artifact_recipe_or_meal_plan_pct</t>
+  </si>
+  <si>
+    <t>artifact_academic_paper_or_thesis_pct</t>
+  </si>
+  <si>
+    <t>artifact_plan_or_strategy_pct</t>
+  </si>
+  <si>
+    <t>artifact_marketing_or_social_content_pct</t>
+  </si>
+  <si>
+    <t>artifact_config_or_infra_pct</t>
+  </si>
+  <si>
+    <t>artifact_audio_or_music_pct</t>
+  </si>
+  <si>
+    <t>artifact_advice_or_recommendation_pct</t>
+  </si>
+  <si>
+    <t>artifact_translation_pct</t>
+  </si>
+  <si>
+    <t>artifact_email_or_message_pct</t>
+  </si>
+  <si>
+    <t>artifact_idea_or_brainstorm_pct</t>
   </si>
   <si>
     <t>artifact_ui_or_design_mockup_pct</t>
@@ -95,247 +329,13 @@
     <t>artifact_app_or_website_pct</t>
   </si>
   <si>
-    <t>artifact_other_pct</t>
-  </si>
-  <si>
-    <t>artifact_analysis_or_summary_pct</t>
-  </si>
-  <si>
-    <t>artifact_ml_or_ai_system_pct</t>
-  </si>
-  <si>
-    <t>artifact_marketing_or_social_content_pct</t>
+    <t>artifact_blog_or_article_pct</t>
+  </si>
+  <si>
+    <t>artifact_resume_or_job_application_pct</t>
   </si>
   <si>
     <t>artifact_math_or_calculation_pct</t>
-  </si>
-  <si>
-    <t>artifact_advice_or_recommendation_pct</t>
-  </si>
-  <si>
-    <t>artifact_sql_or_database_query_pct</t>
-  </si>
-  <si>
-    <t>artifact_code_fix_or_debug_pct</t>
-  </si>
-  <si>
-    <t>artifact_chart_or_visualization_pct</t>
-  </si>
-  <si>
-    <t>artifact_email_or_message_pct</t>
-  </si>
-  <si>
-    <t>artifact_image_or_graphic_pct</t>
-  </si>
-  <si>
-    <t>artifact_game_or_interactive_pct</t>
-  </si>
-  <si>
-    <t>artifact_script_or_snippet_pct</t>
-  </si>
-  <si>
-    <t>artifact_blog_or_article_pct</t>
-  </si>
-  <si>
-    <t>artifact_plan_or_strategy_pct</t>
-  </si>
-  <si>
-    <t>artifact_document_or_report_pct</t>
-  </si>
-  <si>
-    <t>artifact_config_or_infra_pct</t>
-  </si>
-  <si>
-    <t>artifact_educational_material_pct</t>
-  </si>
-  <si>
-    <t>artifact_data_or_spreadsheet_pct</t>
-  </si>
-  <si>
-    <t>artifact_none_pct</t>
-  </si>
-  <si>
-    <t>artifact_explanation_or_answer_pct</t>
-  </si>
-  <si>
-    <t>artifact_idea_or_brainstorm_pct</t>
-  </si>
-  <si>
-    <t>artifact_recipe_or_meal_plan_pct</t>
-  </si>
-  <si>
-    <t>artifact_academic_paper_or_thesis_pct</t>
-  </si>
-  <si>
-    <t>artifact_audio_or_music_pct</t>
-  </si>
-  <si>
-    <t>artifact_creative_writing_pct</t>
-  </si>
-  <si>
-    <t>artifact_resume_or_job_application_pct</t>
-  </si>
-  <si>
-    <t>artifact_translation_pct</t>
-  </si>
-  <si>
-    <t>use_case_personal_pct</t>
-  </si>
-  <si>
-    <t>use_case_coursework_pct</t>
-  </si>
-  <si>
-    <t>collaboration_feedback_loop_pct</t>
-  </si>
-  <si>
-    <t>collaboration_bucket_automation_pct</t>
-  </si>
-  <si>
-    <t>pct</t>
-  </si>
-  <si>
-    <t>multitasking_pct</t>
-  </si>
-  <si>
-    <t>human_only_ability_pct</t>
-  </si>
-  <si>
-    <t>collaboration_validation_pct</t>
-  </si>
-  <si>
-    <t>ai_autonomy_mean</t>
-  </si>
-  <si>
-    <t>human_with_ai_time_mean</t>
-  </si>
-  <si>
-    <t>collaboration_learning_pct</t>
-  </si>
-  <si>
-    <t>ai_education_years_mean</t>
-  </si>
-  <si>
-    <t>use_case_work_pct</t>
-  </si>
-  <si>
-    <t>human_education_years_mean</t>
-  </si>
-  <si>
-    <t>collaboration_task_iteration_pct</t>
-  </si>
-  <si>
-    <t>usage_pct</t>
-  </si>
-  <si>
-    <t>collaboration_bucket_augmentation_pct</t>
-  </si>
-  <si>
-    <t>collaboration_none_pct</t>
-  </si>
-  <si>
-    <t>human_only_time_mean</t>
-  </si>
-  <si>
-    <t>usage_per_capita_index</t>
-  </si>
-  <si>
-    <t>collaboration_directive_pct</t>
-  </si>
-  <si>
-    <t>artifact_resume_or_job_application_pct</t>
-  </si>
-  <si>
-    <t>artifact_idea_or_brainstorm_pct</t>
-  </si>
-  <si>
-    <t>artifact_translation_pct</t>
-  </si>
-  <si>
-    <t>artifact_none_pct</t>
-  </si>
-  <si>
-    <t>artifact_other_pct</t>
-  </si>
-  <si>
-    <t>artifact_ml_or_ai_system_pct</t>
-  </si>
-  <si>
-    <t>artifact_data_or_spreadsheet_pct</t>
-  </si>
-  <si>
-    <t>artifact_chart_or_visualization_pct</t>
-  </si>
-  <si>
-    <t>artifact_video_or_animation_pct</t>
-  </si>
-  <si>
-    <t>artifact_code_fix_or_debug_pct</t>
-  </si>
-  <si>
-    <t>artifact_recipe_or_meal_plan_pct</t>
-  </si>
-  <si>
-    <t>artifact_script_or_snippet_pct</t>
-  </si>
-  <si>
-    <t>artifact_explanation_or_answer_pct</t>
-  </si>
-  <si>
-    <t>artifact_email_or_message_pct</t>
-  </si>
-  <si>
-    <t>artifact_academic_paper_or_thesis_pct</t>
-  </si>
-  <si>
-    <t>artifact_presentation_or_slides_pct</t>
-  </si>
-  <si>
-    <t>artifact_analysis_or_summary_pct</t>
-  </si>
-  <si>
-    <t>artifact_math_or_calculation_pct</t>
-  </si>
-  <si>
-    <t>artifact_marketing_or_social_content_pct</t>
-  </si>
-  <si>
-    <t>artifact_game_or_interactive_pct</t>
-  </si>
-  <si>
-    <t>artifact_educational_material_pct</t>
-  </si>
-  <si>
-    <t>artifact_blog_or_article_pct</t>
-  </si>
-  <si>
-    <t>artifact_document_or_report_pct</t>
-  </si>
-  <si>
-    <t>artifact_ui_or_design_mockup_pct</t>
-  </si>
-  <si>
-    <t>artifact_creative_writing_pct</t>
-  </si>
-  <si>
-    <t>artifact_app_or_website_pct</t>
-  </si>
-  <si>
-    <t>artifact_image_or_graphic_pct</t>
-  </si>
-  <si>
-    <t>artifact_advice_or_recommendation_pct</t>
-  </si>
-  <si>
-    <t>artifact_audio_or_music_pct</t>
-  </si>
-  <si>
-    <t>artifact_sql_or_database_query_pct</t>
-  </si>
-  <si>
-    <t>artifact_config_or_infra_pct</t>
-  </si>
-  <si>
-    <t>artifact_plan_or_strategy_pct</t>
   </si>
   <si>
     <t>source</t>
@@ -634,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>2</v>
+        <v>9645</v>
       </c>
       <c r="E2" s="1">
         <v>21</v>
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>9644</v>
+        <v>9565</v>
       </c>
       <c r="E3" s="1">
         <v>21</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>9645</v>
+        <v>9643</v>
       </c>
       <c r="E4" s="1">
         <v>21</v>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>9644</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>21</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <v>9644</v>
+        <v>9643</v>
       </c>
       <c r="E6" s="1">
         <v>21</v>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>9645</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
         <v>21</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>9638</v>
+        <v>9645</v>
       </c>
       <c r="E8" s="1">
         <v>21</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>9643</v>
+        <v>9644</v>
       </c>
       <c r="E9" s="1">
         <v>21</v>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>9643</v>
+        <v>9645</v>
       </c>
       <c r="E10" s="1">
         <v>21</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>9643</v>
+        <v>9565</v>
       </c>
       <c r="E12" s="1">
         <v>21</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>9643</v>
+        <v>9644</v>
       </c>
       <c r="E13" s="1">
         <v>21</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <v>9565</v>
+        <v>9645</v>
       </c>
       <c r="E14" s="1">
         <v>21</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>9565</v>
+        <v>9638</v>
       </c>
       <c r="E15" s="1">
         <v>21</v>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>9636</v>
       </c>
       <c r="E16" s="1">
         <v>21</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="1">
-        <v>9636</v>
+        <v>9643</v>
       </c>
       <c r="E19" s="1">
         <v>21</v>
@@ -957,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="1">
-        <v>9645</v>
+        <v>9643</v>
       </c>
       <c r="E21" s="1">
         <v>21</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="1">
-        <v>9645</v>
+        <v>9644</v>
       </c>
       <c r="E22" s="1">
         <v>21</v>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="1">
-        <v>22043</v>
+        <v>22061</v>
       </c>
       <c r="E57" s="1">
         <v>21</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="D58" s="1">
-        <v>21809</v>
+        <v>22061</v>
       </c>
       <c r="E58" s="1">
         <v>21</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="1">
-        <v>532491</v>
+        <v>22061</v>
       </c>
       <c r="E59" s="1">
         <v>21</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="1">
-        <v>22061</v>
+        <v>22043</v>
       </c>
       <c r="E60" s="1">
         <v>21</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="1">
-        <v>22060</v>
+        <v>339</v>
       </c>
       <c r="E61" s="1">
         <v>21</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="1">
-        <v>22043</v>
+        <v>22060</v>
       </c>
       <c r="E62" s="1">
         <v>21</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="1">
-        <v>22060</v>
+        <v>22038</v>
       </c>
       <c r="E63" s="1">
         <v>21</v>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="1">
-        <v>22038</v>
+        <v>22060</v>
       </c>
       <c r="E64" s="1">
         <v>21</v>
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="1">
-        <v>22043</v>
+        <v>21809</v>
       </c>
       <c r="E65" s="1">
         <v>21</v>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="1">
-        <v>22060</v>
+        <v>22043</v>
       </c>
       <c r="E66" s="1">
         <v>21</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="1">
-        <v>22061</v>
+        <v>532491</v>
       </c>
       <c r="E67" s="1">
         <v>21</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="1">
-        <v>22061</v>
+        <v>22043</v>
       </c>
       <c r="E68" s="1">
         <v>21</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="1">
-        <v>22043</v>
+        <v>22060</v>
       </c>
       <c r="E69" s="1">
         <v>21</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="1">
-        <v>1421</v>
+        <v>22043</v>
       </c>
       <c r="E70" s="1">
         <v>21</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="1">
-        <v>21809</v>
+        <v>1421</v>
       </c>
       <c r="E71" s="1">
         <v>21</v>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="1">
-        <v>339</v>
+        <v>22043</v>
       </c>
       <c r="E74" s="1">
         <v>21</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="1">
-        <v>22043</v>
+        <v>21809</v>
       </c>
       <c r="E75" s="1">
         <v>21</v>
@@ -5106,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>78.510000000000048</v>
+        <v>78.510000000000034</v>
       </c>
       <c r="G3" s="1">
         <v>647</v>
@@ -5115,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1">
-        <v>81.320000000000093</v>
+        <v>81.320000000000135</v>
       </c>
     </row>
     <row r="4">
@@ -5135,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>88.819999999999979</v>
+        <v>88.820000000000007</v>
       </c>
       <c r="G4" s="1">
         <v>297</v>
@@ -5144,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>90.360000000000014</v>
+        <v>90.360000000000085</v>
       </c>
     </row>
     <row r="5">
@@ -5173,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>98.499999999999986</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="6">
@@ -5222,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>92.230000000000061</v>
+        <v>92.230000000000032</v>
       </c>
       <c r="G7" s="1">
         <v>625</v>
@@ -5231,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>94.610000000000042</v>
+        <v>94.61000000000007</v>
       </c>
     </row>
     <row r="8">
@@ -5251,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>96.690000000000012</v>
+        <v>96.689999999999984</v>
       </c>
       <c r="G8" s="1">
         <v>166</v>
@@ -5260,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>98.410000000000053</v>
+        <v>98.410000000000039</v>
       </c>
     </row>
     <row r="9">
@@ -5280,7 +5280,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>97.110000000000014</v>
+        <v>97.110000000000028</v>
       </c>
       <c r="G9" s="1">
         <v>20</v>
@@ -5289,7 +5289,7 @@
         <v>19</v>
       </c>
       <c r="I9" s="1">
-        <v>98.719999999999985</v>
+        <v>98.71999999999997</v>
       </c>
     </row>
     <row r="10">
@@ -5309,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>96.159999999999954</v>
+        <v>96.159999999999982</v>
       </c>
       <c r="G10" s="1">
         <v>424</v>
@@ -5318,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="1">
-        <v>98.080000000000112</v>
+        <v>98.080000000000098</v>
       </c>
     </row>
     <row r="11">
@@ -5338,7 +5338,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="1">
-        <v>97.36999999999999</v>
+        <v>97.370000000000005</v>
       </c>
       <c r="G11" s="1">
         <v>22</v>
